--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שרית חדד - Mamma Mia</v>
+        <v>שלום ממן - יא רייח</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410015&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410031&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שרית חדד - Mamma Mia</v>
+        <v>שלום ממן - יא רייח</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שראל סופר - מדויק ולא בערך</v>
+        <v>שלו משען - אגם של טעויות</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410014&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410030&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שראל סופר - מדויק ולא בערך</v>
+        <v>שלו משען - אגם של טעויות</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שמוליק סוכות - אבא טוב</v>
+        <v>שיר מזרחי &amp; משה זאודה - יש לנו כאב</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410013&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410029&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שמוליק סוכות - אבא טוב</v>
+        <v>שיר מזרחי &amp; משה זאודה - יש לנו כאב</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שירה ואן ופרן - ייפול עליי</v>
+        <v>קיליאן ג'אמי - צלקת</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410012&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410028&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שירה ואן ופרן - ייפול עליי</v>
+        <v>קיליאן ג'אמי - צלקת</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>רון דבני - מה אני אגיד לך</v>
+        <v>צחי אלוש - טיקי טקה</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410011&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410027&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>רון דבני - מה אני אגיד לך</v>
+        <v>צחי אלוש - טיקי טקה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>נטע ברזילי - גם זה יגיע</v>
+        <v>עידן משה - ריגוש וכאב</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410010&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410026&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>נטע ברזילי - גם זה יגיע</v>
+        <v>עידן משה - ריגוש וכאב</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>מאי כהן - אנשים</v>
+        <v>עידו כנפי - פרפרים בבטן</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410009&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410025&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>מאי כהן - אנשים</v>
+        <v>עידו כנפי - פרפרים בבטן</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>איציק סנדרוי - תנו לי אוויר</v>
+        <v>סגיב כהן - חסד יסובבנו</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410008&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410024&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>איציק סנדרוי - תנו לי אוויר</v>
+        <v>סגיב כהן - חסד יסובבנו</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אהרון סיטבון - ניגון יהודי</v>
+        <v>נתנאל מלכה - בלעדייך</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410007&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410023&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אהרון סיטבון - ניגון יהודי</v>
+        <v>נתנאל מלכה - בלעדייך</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אבישי אזיקרי - לימונדה</v>
+        <v>מיכה ינון - מחרוזת חזון אחרית הימים 2026</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410006&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410022&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אבישי אזיקרי - לימונדה</v>
+        <v>מיכה ינון - מחרוזת חזון אחרית הימים 2026</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>אבי אילסון - בזכותם</v>
+        <v>יהורם גאון - עד עולם</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410005&amp;sid=64ffd39bf093175dd74966d37c559395</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410021&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -849,12 +849,164 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>אבי אילסון - בזכותם</v>
+        <v>יהורם גאון - עד עולם</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410020&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>גבריאל שרם - שוברת גלים</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410019&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>גבריאל שרם - שוברת גלים</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אורי ספז - תפילה שלך</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410018&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אורי ספז - תפילה שלך</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אבי שפרונג - הבית שלי</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410017&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אבי שפרונג - הבית שלי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלום ממן - יא רייח</v>
+        <v>שרון זריהן - רק תזכרי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410031&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410040&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלום ממן - יא רייח</v>
+        <v>שרון זריהן - רק תזכרי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שלו משען - אגם של טעויות</v>
+        <v>עילי בוטנר והילדים החדשים - בוא לאור</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410030&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410039&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שלו משען - אגם של טעויות</v>
+        <v>עילי בוטנר והילדים החדשים - בוא לאור</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שיר מזרחי &amp; משה זאודה - יש לנו כאב</v>
+        <v>נופר נחמני - משמעות</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410029&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410038&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שיר מזרחי &amp; משה זאודה - יש לנו כאב</v>
+        <v>נופר נחמני - משמעות</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>קיליאן ג'אמי - צלקת</v>
+        <v>נהוראי זנטי - מי מספר לך</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410028&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410037&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>קיליאן ג'אמי - צלקת</v>
+        <v>נהוראי זנטי - מי מספר לך</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>צחי אלוש - טיקי טקה</v>
+        <v>מור נדין - נזכרת בעבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410027&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410036&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>צחי אלוש - טיקי טקה</v>
+        <v>מור נדין - נזכרת בעבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>עידן משה - ריגוש וכאב</v>
+        <v>לינוי כהן - עד הסוף</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410026&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410035&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>עידן משה - ריגוש וכאב</v>
+        <v>לינוי כהן - עד הסוף</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>עידו כנפי - פרפרים בבטן</v>
+        <v>גל ג'ומה - קוקוריקו</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410025&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410034&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>עידו כנפי - פרפרים בבטן</v>
+        <v>גל ג'ומה - קוקוריקו</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>סגיב כהן - חסד יסובבנו</v>
+        <v>ג'ולייטה - אמא שלי</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410024&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410033&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>סגיב כהן - חסד יסובבנו</v>
+        <v>ג'ולייטה - אמא שלי</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>נתנאל מלכה - בלעדייך</v>
+        <v>אופק כהן - ברגעים שהתפרקתי</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410023&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410032&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,240 +773,12 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>נתנאל מלכה - בלעדייך</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>מיכה ינון - מחרוזת חזון אחרית הימים 2026</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410022&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>מיכה ינון - מחרוזת חזון אחרית הימים 2026</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>יהורם גאון - עד עולם</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410021&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>יהורם גאון - עד עולם</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410020&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>גבריאל שרם - שוברת גלים</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410019&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>גבריאל שרם - שוברת גלים</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>אורי ספז - תפילה שלך</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410018&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>אורי ספז - תפילה שלך</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>אבי שפרונג - הבית שלי</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410017&amp;sid=ffdf5a86de96ff39379f883bfca9bcca</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v>אבי שפרונג - הבית שלי</v>
+        <v>אופק כהן - ברגעים שהתפרקתי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שרון זריהן - רק תזכרי</v>
+        <v>תמר כהנא - לנצנץ</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-17</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410040&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410041&amp;sid=abad36e6439a3c11a22b9564f2a3015c</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,316 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שרון זריהן - רק תזכרי</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>עילי בוטנר והילדים החדשים - בוא לאור</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410039&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>עילי בוטנר והילדים החדשים - בוא לאור</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>נופר נחמני - משמעות</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410038&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>נופר נחמני - משמעות</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>נהוראי זנטי - מי מספר לך</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410037&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>נהוראי זנטי - מי מספר לך</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>מור נדין - נזכרת בעבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410036&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>מור נדין - נזכרת בעבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>לינוי כהן - עד הסוף</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410035&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>לינוי כהן - עד הסוף</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>גל ג'ומה - קוקוריקו</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410034&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>גל ג'ומה - קוקוריקו</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>ג'ולייטה - אמא שלי</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410033&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>ג'ולייטה - אמא שלי</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אופק כהן - ברגעים שהתפרקתי</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410032&amp;sid=1318ce939be672e5827fe3d26c7987b5</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אופק כהן - ברגעים שהתפרקתי</v>
+        <v>תמר כהנא - לנצנץ</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמר כהנא - לנצנץ</v>
+        <v>מוישי פרסברגר - מחרוזת דיבורים של אמונה 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410041&amp;sid=abad36e6439a3c11a22b9564f2a3015c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410047&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-18</v>
@@ -469,12 +469,202 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמר כהנא - לנצנץ</v>
+        <v>מוישי פרסברגר - מחרוזת דיבורים של אמונה 2026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ליאם דיין - שקט בלב</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410046&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>ליאם דיין - שקט בלב</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>יוסי פריד - איך קען</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410045&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>יוסי פריד - איך קען</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>יובל מזרחי - דואט</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410044&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>יובל מזרחי - דואט</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>דניאל נורני - גלגולים</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410043&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>דניאל נורני - גלגולים</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אמיר אליהו - מחרוזת הלל 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410042&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אמיר אליהו - מחרוזת הלל 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מוישי פרסברגר - מחרוזת דיבורים של אמונה 2026</v>
+        <v>פינחס מלך - אוֹר הָאַהֲבָה הָאֱלֹהִית</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-18</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410047&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410050&amp;sid=0f9be58e618ad79684191ea4a57e6593</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מוישי פרסברגר - מחרוזת דיבורים של אמונה 2026</v>
+        <v>פינחס מלך - אוֹר הָאַהֲבָה הָאֱלֹהִית</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ליאם דיין - שקט בלב</v>
+        <v>עלי הרטום - צוק</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-18</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410046&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410049&amp;sid=0f9be58e618ad79684191ea4a57e6593</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ליאם דיין - שקט בלב</v>
+        <v>עלי הרטום - צוק</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יוסי פריד - איך קען</v>
+        <v>עידן דוכן - מסע רגשי</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-18</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410045&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410048&amp;sid=0f9be58e618ad79684191ea4a57e6593</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,126 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יוסי פריד - איך קען</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>יובל מזרחי - דואט</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410044&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>יובל מזרחי - דואט</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>דניאל נורני - גלגולים</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410043&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>דניאל נורני - גלגולים</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אמיר אליהו - מחרוזת הלל 2026</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410042&amp;sid=280407f62833e0c339548612e2fd2cd7</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אמיר אליהו - מחרוזת הלל 2026</v>
+        <v>עידן דוכן - מסע רגשי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פינחס מלך - אוֹר הָאַהֲבָה הָאֱלֹהִית</v>
+        <v>אשר גבאי - שירת המונים - אחת שאלתי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410050&amp;sid=0f9be58e618ad79684191ea4a57e6593</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410056&amp;sid=746bcaca46b314a4372c05f7bdb94eaa</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-19</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פינחס מלך - אוֹר הָאַהֲבָה הָאֱלֹהִית</v>
+        <v>אשר גבאי - שירת המונים - אחת שאלתי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עלי הרטום - צוק</v>
+        <v>אדווה עומר - רק אלייך</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410049&amp;sid=0f9be58e618ad79684191ea4a57e6593</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410055&amp;sid=746bcaca46b314a4372c05f7bdb94eaa</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-19</v>
@@ -507,50 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עלי הרטום - צוק</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>עידן דוכן - מסע רגשי</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410048&amp;sid=0f9be58e618ad79684191ea4a57e6593</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>עידן דוכן - מסע רגשי</v>
+        <v>אדווה עומר - רק אלייך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אשר גבאי - שירת המונים - אחת שאלתי</v>
+        <v>מכלוף - תשמור עליי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410056&amp;sid=746bcaca46b314a4372c05f7bdb94eaa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410064&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-19</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אשר גבאי - שירת המונים - אחת שאלתי</v>
+        <v>מכלוף - תשמור עליי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אדווה עומר - רק אלייך</v>
+        <v>מיקי בן עטר - מחרוזת מזמורי שבת 2026</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-19</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410055&amp;sid=746bcaca46b314a4372c05f7bdb94eaa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410063&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-19</v>
@@ -507,12 +507,240 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אדווה עומר - רק אלייך</v>
+        <v>מיקי בן עטר - מחרוזת מזמורי שבת 2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ליאן ניגרין - נפש תאומה קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410062&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>ליאן ניגרין - נפש תאומה קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>יגאל עדי - מחרוזת עגילי זהב 2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410061&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>יגאל עדי - מחרוזת עגילי זהב 2026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>טל לוי - אופוריה משקרת</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410060&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>טל לוי - אופוריה משקרת</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>דורון רוקח - מחרוזת נעורים 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410059&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>דורון רוקח - מחרוזת נעורים 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>דולב שמחי - לילה מאוחר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410058&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>דולב שמחי - לילה מאוחר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>גלית סדן &amp; שר-אל - אם את רווקה 2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410057&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>גלית סדן &amp; שר-אל - אם את רווקה 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מכלוף - תשמור עליי</v>
+        <v>תמר ריילי &amp; לירן דנינו - בת של מלך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410064&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410070&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-19</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מכלוף - תשמור עליי</v>
+        <v>תמר ריילי &amp; לירן דנינו - בת של מלך</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מיקי בן עטר - מחרוזת מזמורי שבת 2026</v>
+        <v>שר-אל - זמן</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-19</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410063&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410069&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-19</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מיקי בן עטר - מחרוזת מזמורי שבת 2026</v>
+        <v>שר-אל - זמן</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ליאן ניגרין - נפש תאומה קאבר</v>
+        <v>שמואל - אני מבורך</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-19</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410062&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410068&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-19</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ליאן ניגרין - נפש תאומה קאבר</v>
+        <v>שמואל - אני מבורך</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יגאל עדי - מחרוזת עגילי זהב 2026</v>
+        <v>שיר לוי - אהבתי באמת</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-19</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410061&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410067&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-19</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יגאל עדי - מחרוזת עגילי זהב 2026</v>
+        <v>שיר לוי - אהבתי באמת</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>טל לוי - אופוריה משקרת</v>
+        <v>רני רחמים - נושאות עיניי תפילה</v>
       </c>
       <c r="B6" t="str">
         <v>2026-03-19</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410060&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410066&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-19</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>טל לוי - אופוריה משקרת</v>
+        <v>רני רחמים - נושאות עיניי תפילה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>דורון רוקח - מחרוזת נעורים 2026</v>
+        <v>רג'ה &amp; נתי אפ אמ - מסובב הסיבות</v>
       </c>
       <c r="B7" t="str">
         <v>2026-03-19</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410059&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410065&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-19</v>
@@ -659,88 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>דורון רוקח - מחרוזת נעורים 2026</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>דולב שמחי - לילה מאוחר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410058&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>דולב שמחי - לילה מאוחר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>גלית סדן &amp; שר-אל - אם את רווקה 2026</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410057&amp;sid=811de4f9ec95ebc290c8d82901e5655f</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>גלית סדן &amp; שר-אל - אם את רווקה 2026</v>
+        <v>רג'ה &amp; נתי אפ אמ - מסובב הסיבות</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמר ריילי &amp; לירן דנינו - בת של מלך</v>
+        <v>רועי שמואלי - נרקומן של רגשות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410070&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410087&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמר ריילי &amp; לירן דנינו - בת של מלך</v>
+        <v>רועי שמואלי - נרקומן של רגשות</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שר-אל - זמן</v>
+        <v>רומי רון - עד שאשוב</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410069&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410086&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שר-אל - זמן</v>
+        <v>רומי רון - עד שאשוב</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שמואל - אני מבורך</v>
+        <v>רוחמה רז - אל האור</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410068&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410085&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שמואל - אני מבורך</v>
+        <v>רוחמה רז - אל האור</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שיר לוי - אהבתי באמת</v>
+        <v>נחמן סבג מארח את פייגה סבג - מחרוזת ממשיך את החיים 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410067&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410084&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שיר לוי - אהבתי באמת</v>
+        <v>נחמן סבג מארח את פייגה סבג - מחרוזת ממשיך את החיים 2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>רני רחמים - נושאות עיניי תפילה</v>
+        <v>משה זרצקי - האמונה נותנת כח</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410066&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410083&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>רני רחמים - נושאות עיניי תפילה</v>
+        <v>משה זרצקי - האמונה נותנת כח</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>רג'ה &amp; נתי אפ אמ - מסובב הסיבות</v>
+        <v>מייק מנג'ו - מחרוזת מלכת המועדון 2026</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410065&amp;sid=d1f963fe2cdb04d44984e4c96de62fe7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410082&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,12 +659,392 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>רג'ה &amp; נתי אפ אמ - מסובב הסיבות</v>
+        <v>מייק מנג'ו - מחרוזת מלכת המועדון 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ישראל ברששת - אהבה כזאת זה אסור</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410081&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>ישראל ברששת - אהבה כזאת זה אסור</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>טל ועקנין - לה לה גם בתקופות הכי קשות</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410080&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>טל ועקנין - לה לה גם בתקופות הכי קשות</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>טל בן גיגי - מאה אלף</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410079&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>טל בן גיגי - מאה אלף</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>חזי כהן - כשהכל נשבר</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410078&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>חזי כהן - כשהכל נשבר</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>חגית וייסלר - בשבילך כמו אלוקים</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410077&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>חגית וייסלר - בשבילך כמו אלוקים</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>דניאל חן - לב אחד (עם ישראל חי)</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410076&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>דניאל חן - לב אחד (עם ישראל חי)</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>בן יוסף דניאל - האריה אם ישאג</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410075&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>בן יוסף דניאל - האריה אם ישאג</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>9 מילימטר - פנטזיות על אימפריה</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410074&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>9 מילימטר - פנטזיות על אימפריה</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אייל גולן - בית מזכוכית</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410073&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אייל גולן - בית מזכוכית</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>אופיר ברמי - אתה המלך</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410072&amp;sid=05206eacbe62b6bb574609b11b437bc0</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>אופיר ברמי - אתה המלך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L17"/>
   </ignoredErrors>
 </worksheet>
 </file>